--- a/2024/tmp/CCA Senior League Division 1.xlsx
+++ b/2024/tmp/CCA Senior League Division 1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="71" count="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="72" count="72">
   <si>
     <t>Division</t>
   </si>
@@ -46,13 +46,13 @@
     <t>CCA Senior League Division 1</t>
   </si>
   <si>
-    <t>117767</t>
-  </si>
-  <si>
-    <t>Horseheath CC - 1st XI</t>
-  </si>
-  <si>
-    <t>134360</t>
+    <t>125381</t>
+  </si>
+  <si>
+    <t>Ramsey CC, Hunts - 2nd XI</t>
+  </si>
+  <si>
+    <t>78071</t>
   </si>
   <si>
     <t>Abington CC, Cambs - 1st XI</t>
@@ -61,40 +61,79 @@
     <t>29732</t>
   </si>
   <si>
-    <t>The Cricket Meadow, Howards Lane</t>
-  </si>
-  <si>
-    <t>2024/08/10</t>
+    <t>The Cricketfield</t>
+  </si>
+  <si>
+    <t>14834</t>
+  </si>
+  <si>
+    <t>2025/08/09</t>
   </si>
   <si>
     <t>13:00</t>
   </si>
   <si>
+    <t>Bluntisham CC - 1st XI</t>
+  </si>
+  <si>
+    <t>41728</t>
+  </si>
+  <si>
+    <t>2025/08/30</t>
+  </si>
+  <si>
     <t>Wilburton CC - 1st XI</t>
   </si>
   <si>
     <t>60408</t>
   </si>
   <si>
-    <t>2024/06/29</t>
-  </si>
-  <si>
-    <t>Ramsey CC, Hunts - 2nd XI</t>
-  </si>
-  <si>
-    <t>78071</t>
-  </si>
-  <si>
-    <t>2024/06/08</t>
-  </si>
-  <si>
-    <t>Bluntisham CC - 1st XI</t>
-  </si>
-  <si>
-    <t>41728</t>
-  </si>
-  <si>
-    <t>2024/07/13</t>
+    <t>2025/08/02</t>
+  </si>
+  <si>
+    <t>Thriplow CC - 1st XI</t>
+  </si>
+  <si>
+    <t>51520</t>
+  </si>
+  <si>
+    <t>2025/05/31</t>
+  </si>
+  <si>
+    <t>Cambridge Old Monks CC - 1st XI</t>
+  </si>
+  <si>
+    <t>323460</t>
+  </si>
+  <si>
+    <t>2025/07/19</t>
+  </si>
+  <si>
+    <t>Audley Wenden CC - 1st XI</t>
+  </si>
+  <si>
+    <t>377531</t>
+  </si>
+  <si>
+    <t>2025/08/16</t>
+  </si>
+  <si>
+    <t>Histon CC - 2nd XI</t>
+  </si>
+  <si>
+    <t>18967</t>
+  </si>
+  <si>
+    <t>2025/05/24</t>
+  </si>
+  <si>
+    <t>Longstanton Grasshoppers CC - 1st XI</t>
+  </si>
+  <si>
+    <t>12244</t>
+  </si>
+  <si>
+    <t>2025/05/10</t>
   </si>
   <si>
     <t>Fulbourn Institute CC - 1st XI</t>
@@ -103,43 +142,31 @@
     <t>32550</t>
   </si>
   <si>
-    <t>2024/05/18</t>
-  </si>
-  <si>
-    <t>City of Ely CC - 1st XI</t>
-  </si>
-  <si>
-    <t>23142</t>
-  </si>
-  <si>
-    <t>2024/05/25</t>
-  </si>
-  <si>
-    <t>Longstanton Grasshoppers CC - 1st XI</t>
-  </si>
-  <si>
-    <t>12244</t>
-  </si>
-  <si>
-    <t>2024/06/15</t>
-  </si>
-  <si>
-    <t>Wisbech Town CC - 2nd XI</t>
-  </si>
-  <si>
-    <t>14510</t>
-  </si>
-  <si>
-    <t>2024/08/31</t>
-  </si>
-  <si>
-    <t>Thriplow CC - 1st XI</t>
-  </si>
-  <si>
-    <t>51520</t>
-  </si>
-  <si>
-    <t>2024/05/11</t>
+    <t>2025/06/21</t>
+  </si>
+  <si>
+    <t>Longstanton Recreation Ground</t>
+  </si>
+  <si>
+    <t>12312</t>
+  </si>
+  <si>
+    <t>2025/05/03</t>
+  </si>
+  <si>
+    <t>2025/08/23</t>
+  </si>
+  <si>
+    <t>2025/07/12</t>
+  </si>
+  <si>
+    <t>2025/06/14</t>
+  </si>
+  <si>
+    <t>2025/07/05</t>
+  </si>
+  <si>
+    <t>2025/05/17</t>
   </si>
   <si>
     <t>Fulbourn Recreation Ground</t>
@@ -148,28 +175,28 @@
     <t>9770</t>
   </si>
   <si>
-    <t>2024/07/20</t>
-  </si>
-  <si>
-    <t>2024/07/06</t>
-  </si>
-  <si>
-    <t>2024/08/17</t>
-  </si>
-  <si>
-    <t>2024/06/22</t>
-  </si>
-  <si>
-    <t>Wisbech Town CC</t>
-  </si>
-  <si>
-    <t>11646</t>
-  </si>
-  <si>
-    <t>2024/06/01</t>
-  </si>
-  <si>
-    <t>2024/08/24</t>
+    <t>2025/06/28</t>
+  </si>
+  <si>
+    <t>Bluntisham Recreation Ground</t>
+  </si>
+  <si>
+    <t>13076</t>
+  </si>
+  <si>
+    <t>2025/07/26</t>
+  </si>
+  <si>
+    <t>2025/06/07</t>
+  </si>
+  <si>
+    <t>Histon Recreation Ground</t>
+  </si>
+  <si>
+    <t>10999</t>
+  </si>
+  <si>
+    <t>2025/09/06</t>
   </si>
   <si>
     <t>The Piece Ground</t>
@@ -178,52 +205,28 @@
     <t>2191</t>
   </si>
   <si>
-    <t>2024/05/04</t>
-  </si>
-  <si>
-    <t>2024/07/27</t>
-  </si>
-  <si>
-    <t>Bluntisham Recreation Ground</t>
-  </si>
-  <si>
-    <t>13076</t>
-  </si>
-  <si>
-    <t>2024/08/03</t>
+    <t>AEH</t>
+  </si>
+  <si>
+    <t>Wendon</t>
+  </si>
+  <si>
+    <t>Calford Green</t>
+  </si>
+  <si>
+    <t>58898</t>
+  </si>
+  <si>
+    <t>Abington Cricket Ground</t>
+  </si>
+  <si>
+    <t>13558</t>
   </si>
   <si>
     <t>Thriplow</t>
   </si>
   <si>
     <t>4585</t>
-  </si>
-  <si>
-    <t>The Cricketfield</t>
-  </si>
-  <si>
-    <t>14834</t>
-  </si>
-  <si>
-    <t>2024/04/27</t>
-  </si>
-  <si>
-    <t>Abington Cricket Ground</t>
-  </si>
-  <si>
-    <t>13558</t>
-  </si>
-  <si>
-    <t>The Paradise Centre</t>
-  </si>
-  <si>
-    <t>25056</t>
-  </si>
-  <si>
-    <t>Longstanton Recreation Ground</t>
-  </si>
-  <si>
-    <t>12312</t>
   </si>
 </sst>
 </file>
@@ -265,7 +268,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="2" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -287,14 +290,17 @@
       <c r="G2" t="s">
         <v>16</v>
       </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" x14ac:dyDescent="0.25" spans="1:9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -308,22 +314,25 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
       </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" x14ac:dyDescent="0.25" spans="1:9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -337,22 +346,25 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
         <v>16</v>
       </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" x14ac:dyDescent="0.25" spans="1:9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -366,22 +378,25 @@
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
         <v>16</v>
       </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" x14ac:dyDescent="0.25" spans="1:9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -395,22 +410,25 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
         <v>16</v>
       </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" x14ac:dyDescent="0.25" spans="1:9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -424,22 +442,25 @@
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" t="s">
         <v>16</v>
       </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" x14ac:dyDescent="0.25" spans="1:9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -453,22 +474,25 @@
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
         <v>16</v>
       </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
       <c r="I8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" x14ac:dyDescent="0.25" spans="1:9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -482,22 +506,25 @@
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
         <v>16</v>
       </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
       <c r="I9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" x14ac:dyDescent="0.25" spans="1:9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -511,19 +538,22 @@
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
         <v>16</v>
       </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.25" spans="1:10">
@@ -534,28 +564,28 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.25" spans="1:10">
@@ -566,28 +596,28 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.25" spans="1:10">
@@ -598,28 +628,28 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
         <v>29</v>
       </c>
-      <c r="E13" t="s">
-        <v>40</v>
-      </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I13" t="s">
         <v>47</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.25" spans="1:10">
@@ -630,28 +660,28 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.25" spans="1:10">
@@ -662,28 +692,28 @@
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I15" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.25" spans="1:10">
@@ -694,28 +724,28 @@
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" t="s">
         <v>43</v>
       </c>
-      <c r="H16" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" t="s">
-        <v>24</v>
-      </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.25" spans="1:10">
@@ -726,28 +756,28 @@
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I17" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25" spans="1:10">
@@ -758,28 +788,28 @@
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" x14ac:dyDescent="0.25" spans="1:10">
@@ -790,28 +820,28 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25" spans="1:10">
@@ -822,28 +852,28 @@
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I20" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" x14ac:dyDescent="0.25" spans="1:10">
@@ -854,28 +884,28 @@
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I21" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" x14ac:dyDescent="0.25" spans="1:10">
@@ -886,28 +916,28 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G22" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H22" t="s">
+        <v>53</v>
+      </c>
+      <c r="I22" t="s">
         <v>50</v>
       </c>
-      <c r="I22" t="s">
-        <v>21</v>
-      </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" x14ac:dyDescent="0.25" spans="1:10">
@@ -918,28 +948,28 @@
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E23" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H23" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I23" t="s">
         <v>46</v>
       </c>
       <c r="J23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" x14ac:dyDescent="0.25" spans="1:10">
@@ -950,28 +980,28 @@
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F24" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H24" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I24" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="J24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" x14ac:dyDescent="0.25" spans="1:10">
@@ -982,28 +1012,28 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" t="s">
         <v>38</v>
       </c>
-      <c r="E25" t="s">
-        <v>12</v>
-      </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H25" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I25" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="J25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" x14ac:dyDescent="0.25" spans="1:10">
@@ -1014,28 +1044,28 @@
         <v>11</v>
       </c>
       <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" t="s">
         <v>37</v>
       </c>
-      <c r="D26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H26" t="s">
-        <v>50</v>
-      </c>
-      <c r="I26" t="s">
-        <v>51</v>
-      </c>
       <c r="J26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25" spans="1:10">
@@ -1046,28 +1076,28 @@
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E27" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G27" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H27" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I27" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" x14ac:dyDescent="0.25" spans="1:10">
@@ -1078,28 +1108,28 @@
         <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G28" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H28" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I28" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25" spans="1:10">
@@ -1110,28 +1140,28 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H29" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I29" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="J29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" x14ac:dyDescent="0.25" spans="1:10">
@@ -1142,28 +1172,28 @@
         <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G30" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H30" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I30" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="J30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" x14ac:dyDescent="0.25" spans="1:10">
@@ -1174,28 +1204,28 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G31" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H31" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I31" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25" spans="1:10">
@@ -1206,28 +1236,28 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G32" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H32" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I32" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="J32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25" spans="1:10">
@@ -1238,28 +1268,28 @@
         <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H33" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="J33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.25" spans="1:10">
@@ -1270,28 +1300,28 @@
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F34" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I34" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25" spans="1:10">
@@ -1302,28 +1332,28 @@
         <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F35" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H35" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I35" t="s">
         <v>46</v>
       </c>
       <c r="J35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25" spans="1:10">
@@ -1334,28 +1364,28 @@
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F36" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H36" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I36" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25" spans="1:10">
@@ -1366,28 +1396,28 @@
         <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H37" t="s">
+        <v>56</v>
+      </c>
+      <c r="I37" t="s">
         <v>54</v>
       </c>
-      <c r="I37" t="s">
-        <v>47</v>
-      </c>
       <c r="J37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" x14ac:dyDescent="0.25" spans="1:10">
@@ -1398,28 +1428,28 @@
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F38" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G38" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H38" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I38" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25" spans="1:10">
@@ -1430,28 +1460,28 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E39" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F39" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G39" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I39" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" x14ac:dyDescent="0.25" spans="1:10">
@@ -1462,28 +1492,28 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D40" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G40" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H40" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I40" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="J40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" x14ac:dyDescent="0.25" spans="1:10">
@@ -1494,28 +1524,28 @@
         <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D41" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G41" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I41" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="J41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" x14ac:dyDescent="0.25" spans="1:10">
@@ -1526,28 +1556,28 @@
         <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D42" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" t="s">
         <v>26</v>
       </c>
-      <c r="E42" t="s">
-        <v>34</v>
-      </c>
       <c r="F42" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G42" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I42" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="J42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" x14ac:dyDescent="0.25" spans="1:10">
@@ -1558,28 +1588,28 @@
         <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D43" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F43" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G43" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H43" t="s">
+        <v>60</v>
+      </c>
+      <c r="I43" t="s">
         <v>58</v>
       </c>
-      <c r="I43" t="s">
-        <v>46</v>
-      </c>
       <c r="J43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" x14ac:dyDescent="0.25" spans="1:10">
@@ -1590,28 +1620,28 @@
         <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D44" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E44" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F44" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G44" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" x14ac:dyDescent="0.25" spans="1:10">
@@ -1622,28 +1652,28 @@
         <v>11</v>
       </c>
       <c r="C45" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" t="s">
+        <v>59</v>
+      </c>
+      <c r="H45" t="s">
+        <v>60</v>
+      </c>
+      <c r="I45" t="s">
         <v>25</v>
       </c>
-      <c r="D45" t="s">
-        <v>26</v>
-      </c>
-      <c r="E45" t="s">
-        <v>37</v>
-      </c>
-      <c r="F45" t="s">
-        <v>38</v>
-      </c>
-      <c r="G45" t="s">
-        <v>57</v>
-      </c>
-      <c r="H45" t="s">
-        <v>58</v>
-      </c>
-      <c r="I45" t="s">
-        <v>59</v>
-      </c>
       <c r="J45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" x14ac:dyDescent="0.25" spans="1:10">
@@ -1654,28 +1684,28 @@
         <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D46" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E46" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s">
+        <v>59</v>
+      </c>
+      <c r="H46" t="s">
+        <v>60</v>
+      </c>
+      <c r="I46" t="s">
         <v>40</v>
       </c>
-      <c r="F46" t="s">
-        <v>41</v>
-      </c>
-      <c r="G46" t="s">
-        <v>57</v>
-      </c>
-      <c r="H46" t="s">
-        <v>58</v>
-      </c>
-      <c r="I46" t="s">
-        <v>30</v>
-      </c>
       <c r="J46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" x14ac:dyDescent="0.25" spans="1:10">
@@ -1686,28 +1716,28 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F47" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H47" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I47" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" x14ac:dyDescent="0.25" spans="1:10">
@@ -1718,28 +1748,28 @@
         <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
+        <v>35</v>
+      </c>
+      <c r="F48" t="s">
+        <v>36</v>
+      </c>
+      <c r="G48" t="s">
+        <v>62</v>
+      </c>
+      <c r="H48" t="s">
+        <v>63</v>
+      </c>
+      <c r="I48" t="s">
         <v>22</v>
       </c>
-      <c r="F48" t="s">
-        <v>23</v>
-      </c>
-      <c r="G48" t="s">
-        <v>60</v>
-      </c>
-      <c r="H48" t="s">
-        <v>61</v>
-      </c>
-      <c r="I48" t="s">
-        <v>55</v>
-      </c>
       <c r="J48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" x14ac:dyDescent="0.25" spans="1:10">
@@ -1750,28 +1780,28 @@
         <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D49" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F49" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G49" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H49" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I49" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="J49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" x14ac:dyDescent="0.25" spans="1:10">
@@ -1782,28 +1812,28 @@
         <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D50" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G50" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H50" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I50" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" x14ac:dyDescent="0.25" spans="1:10">
@@ -1814,28 +1844,28 @@
         <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G51" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H51" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I51" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" x14ac:dyDescent="0.25" spans="1:10">
@@ -1846,28 +1876,28 @@
         <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F52" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G52" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H52" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I52" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="J52" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" x14ac:dyDescent="0.25" spans="1:10">
@@ -1878,28 +1908,28 @@
         <v>11</v>
       </c>
       <c r="C53" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D53" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H53" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I53" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="J53" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" x14ac:dyDescent="0.25" spans="1:10">
@@ -1910,28 +1940,28 @@
         <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G54" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H54" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I54" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J54" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.25" spans="1:10">
@@ -1942,316 +1972,289 @@
         <v>11</v>
       </c>
       <c r="C55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" t="s">
+        <v>41</v>
+      </c>
+      <c r="F55" t="s">
+        <v>42</v>
+      </c>
+      <c r="G55" t="s">
+        <v>62</v>
+      </c>
+      <c r="H55" t="s">
+        <v>63</v>
+      </c>
+      <c r="I55" t="s">
         <v>40</v>
       </c>
-      <c r="D55" t="s">
+      <c r="J55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" t="s">
+        <v>33</v>
+      </c>
+      <c r="E56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s">
+        <v>64</v>
+      </c>
+      <c r="I56" t="s">
+        <v>49</v>
+      </c>
+      <c r="J56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" t="s">
+        <v>33</v>
+      </c>
+      <c r="E57" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" t="s">
+        <v>64</v>
+      </c>
+      <c r="I57" t="s">
+        <v>54</v>
+      </c>
+      <c r="J57" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" t="s">
+        <v>33</v>
+      </c>
+      <c r="E58" t="s">
+        <v>35</v>
+      </c>
+      <c r="F58" t="s">
+        <v>36</v>
+      </c>
+      <c r="G58" t="s">
+        <v>64</v>
+      </c>
+      <c r="I58" t="s">
+        <v>57</v>
+      </c>
+      <c r="J58" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A59" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" t="s">
+        <v>33</v>
+      </c>
+      <c r="E59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F59" t="s">
+        <v>30</v>
+      </c>
+      <c r="G59" t="s">
+        <v>65</v>
+      </c>
+      <c r="I59" t="s">
+        <v>61</v>
+      </c>
+      <c r="J59" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" t="s">
+        <v>33</v>
+      </c>
+      <c r="E60" t="s">
+        <v>26</v>
+      </c>
+      <c r="F60" t="s">
+        <v>27</v>
+      </c>
+      <c r="G60" t="s">
+        <v>64</v>
+      </c>
+      <c r="I60" t="s">
+        <v>43</v>
+      </c>
+      <c r="J60" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A61" t="s">
+        <v>10</v>
+      </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" t="s">
+        <v>33</v>
+      </c>
+      <c r="E61" t="s">
+        <v>23</v>
+      </c>
+      <c r="F61" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" t="s">
+        <v>64</v>
+      </c>
+      <c r="I61" t="s">
+        <v>31</v>
+      </c>
+      <c r="J61" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A62" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" t="s">
+        <v>33</v>
+      </c>
+      <c r="E62" t="s">
+        <v>38</v>
+      </c>
+      <c r="F62" t="s">
+        <v>39</v>
+      </c>
+      <c r="G62" t="s">
+        <v>64</v>
+      </c>
+      <c r="I62" t="s">
+        <v>58</v>
+      </c>
+      <c r="J62" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A63" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" t="s">
+        <v>33</v>
+      </c>
+      <c r="E63" t="s">
         <v>41</v>
       </c>
-      <c r="E55" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55" t="s">
-        <v>60</v>
-      </c>
-      <c r="H55" t="s">
-        <v>61</v>
-      </c>
-      <c r="I55" t="s">
+      <c r="F63" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" t="s">
+        <v>64</v>
+      </c>
+      <c r="I63" t="s">
+        <v>48</v>
+      </c>
+      <c r="J63" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A64" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" t="s">
         <v>33</v>
       </c>
-      <c r="J55" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="56" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A56" t="s">
-        <v>10</v>
-      </c>
-      <c r="B56" t="s">
-        <v>11</v>
-      </c>
-      <c r="C56" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56" t="s">
-        <v>23</v>
-      </c>
-      <c r="E56" t="s">
-        <v>40</v>
-      </c>
-      <c r="F56" t="s">
-        <v>41</v>
-      </c>
-      <c r="G56" t="s">
-        <v>62</v>
-      </c>
-      <c r="H56" t="s">
-        <v>63</v>
-      </c>
-      <c r="I56" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A57" t="s">
-        <v>10</v>
-      </c>
-      <c r="B57" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" t="s">
-        <v>22</v>
-      </c>
-      <c r="D57" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" t="s">
-        <v>19</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="E64" t="s">
         <v>20</v>
       </c>
-      <c r="G57" t="s">
-        <v>62</v>
-      </c>
-      <c r="H57" t="s">
-        <v>63</v>
-      </c>
-      <c r="I57" t="s">
-        <v>48</v>
-      </c>
-      <c r="J57" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="58" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A58" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" t="s">
-        <v>11</v>
-      </c>
-      <c r="C58" t="s">
-        <v>22</v>
-      </c>
-      <c r="D58" t="s">
-        <v>23</v>
-      </c>
-      <c r="E58" t="s">
-        <v>37</v>
-      </c>
-      <c r="F58" t="s">
-        <v>38</v>
-      </c>
-      <c r="G58" t="s">
-        <v>62</v>
-      </c>
-      <c r="H58" t="s">
-        <v>63</v>
-      </c>
-      <c r="I58" t="s">
+      <c r="F64" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" t="s">
         <v>64</v>
       </c>
-      <c r="J58" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="59" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A59" t="s">
-        <v>10</v>
-      </c>
-      <c r="B59" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" t="s">
-        <v>22</v>
-      </c>
-      <c r="D59" t="s">
-        <v>23</v>
-      </c>
-      <c r="E59" t="s">
-        <v>12</v>
-      </c>
-      <c r="F59" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" t="s">
-        <v>62</v>
-      </c>
-      <c r="H59" t="s">
-        <v>63</v>
-      </c>
-      <c r="I59" t="s">
-        <v>59</v>
-      </c>
-      <c r="J59" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A60" t="s">
-        <v>10</v>
-      </c>
-      <c r="B60" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" t="s">
-        <v>22</v>
-      </c>
-      <c r="D60" t="s">
-        <v>23</v>
-      </c>
-      <c r="E60" t="s">
-        <v>34</v>
-      </c>
-      <c r="F60" t="s">
-        <v>35</v>
-      </c>
-      <c r="G60" t="s">
-        <v>62</v>
-      </c>
-      <c r="H60" t="s">
-        <v>63</v>
-      </c>
-      <c r="I60" t="s">
-        <v>46</v>
-      </c>
-      <c r="J60" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="61" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A61" t="s">
-        <v>10</v>
-      </c>
-      <c r="B61" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" t="s">
-        <v>22</v>
-      </c>
-      <c r="D61" t="s">
-        <v>23</v>
-      </c>
-      <c r="E61" t="s">
-        <v>28</v>
-      </c>
-      <c r="F61" t="s">
-        <v>29</v>
-      </c>
-      <c r="G61" t="s">
-        <v>62</v>
-      </c>
-      <c r="H61" t="s">
-        <v>63</v>
-      </c>
-      <c r="I61" t="s">
-        <v>51</v>
-      </c>
-      <c r="J61" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="62" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A62" t="s">
-        <v>10</v>
-      </c>
-      <c r="B62" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" t="s">
-        <v>22</v>
-      </c>
-      <c r="D62" t="s">
-        <v>23</v>
-      </c>
-      <c r="E62" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" t="s">
-        <v>62</v>
-      </c>
-      <c r="H62" t="s">
-        <v>63</v>
-      </c>
-      <c r="I62" t="s">
-        <v>33</v>
-      </c>
-      <c r="J62" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="63" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A63" t="s">
-        <v>10</v>
-      </c>
-      <c r="B63" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" t="s">
-        <v>22</v>
-      </c>
-      <c r="D63" t="s">
-        <v>23</v>
-      </c>
-      <c r="E63" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" t="s">
-        <v>15</v>
-      </c>
-      <c r="G63" t="s">
-        <v>62</v>
-      </c>
-      <c r="H63" t="s">
-        <v>63</v>
-      </c>
-      <c r="I63" t="s">
-        <v>45</v>
-      </c>
-      <c r="J63" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="64" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A64" t="s">
-        <v>10</v>
-      </c>
-      <c r="B64" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" t="s">
-        <v>22</v>
-      </c>
-      <c r="D64" t="s">
-        <v>23</v>
-      </c>
-      <c r="E64" t="s">
-        <v>31</v>
-      </c>
-      <c r="F64" t="s">
-        <v>32</v>
-      </c>
-      <c r="G64" t="s">
-        <v>62</v>
-      </c>
-      <c r="H64" t="s">
-        <v>63</v>
-      </c>
       <c r="I64" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J64" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" x14ac:dyDescent="0.25" spans="1:10">
@@ -2262,28 +2265,28 @@
         <v>11</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D65" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E65" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F65" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I65" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="J65" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" x14ac:dyDescent="0.25" spans="1:10">
@@ -2294,28 +2297,28 @@
         <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D66" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E66" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F66" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="G66" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H66" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I66" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J66" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" x14ac:dyDescent="0.25" spans="1:10">
@@ -2326,28 +2329,28 @@
         <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D67" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E67" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F67" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="G67" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H67" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I67" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J67" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" x14ac:dyDescent="0.25" spans="1:10">
@@ -2358,28 +2361,28 @@
         <v>11</v>
       </c>
       <c r="C68" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" t="s">
         <v>14</v>
       </c>
-      <c r="D68" t="s">
+      <c r="F68" t="s">
         <v>15</v>
       </c>
-      <c r="E68" t="s">
-        <v>25</v>
-      </c>
-      <c r="F68" t="s">
-        <v>26</v>
-      </c>
       <c r="G68" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H68" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I68" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J68" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" x14ac:dyDescent="0.25" spans="1:10">
@@ -2390,28 +2393,28 @@
         <v>11</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D69" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G69" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H69" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I69" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="J69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" x14ac:dyDescent="0.25" spans="1:10">
@@ -2422,28 +2425,28 @@
         <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D70" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E70" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F70" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G70" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H70" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I70" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J70" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" x14ac:dyDescent="0.25" spans="1:10">
@@ -2454,28 +2457,28 @@
         <v>11</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E71" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F71" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G71" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H71" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I71" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="J71" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" x14ac:dyDescent="0.25" spans="1:10">
@@ -2486,28 +2489,28 @@
         <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D72" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E72" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F72" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G72" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H72" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I72" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" x14ac:dyDescent="0.25" spans="1:10">
@@ -2518,28 +2521,28 @@
         <v>11</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D73" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E73" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" t="s">
+        <v>33</v>
+      </c>
+      <c r="G73" t="s">
+        <v>66</v>
+      </c>
+      <c r="H73" t="s">
+        <v>67</v>
+      </c>
+      <c r="I73" t="s">
         <v>40</v>
       </c>
-      <c r="F73" t="s">
-        <v>41</v>
-      </c>
-      <c r="G73" t="s">
-        <v>65</v>
-      </c>
-      <c r="H73" t="s">
-        <v>66</v>
-      </c>
-      <c r="I73" t="s">
-        <v>56</v>
-      </c>
       <c r="J73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" x14ac:dyDescent="0.25" spans="1:10">
@@ -2550,28 +2553,28 @@
         <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" t="s">
         <v>32</v>
       </c>
-      <c r="E74" t="s">
-        <v>12</v>
-      </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="G74" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H74" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I74" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="J74" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" x14ac:dyDescent="0.25" spans="1:10">
@@ -2582,28 +2585,28 @@
         <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E75" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F75" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G75" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H75" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I75" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="J75" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" x14ac:dyDescent="0.25" spans="1:10">
@@ -2614,28 +2617,28 @@
         <v>11</v>
       </c>
       <c r="C76" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E76" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F76" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G76" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H76" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I76" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="J76" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" x14ac:dyDescent="0.25" spans="1:10">
@@ -2646,28 +2649,28 @@
         <v>11</v>
       </c>
       <c r="C77" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E77" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F77" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G77" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H77" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I77" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J77" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" x14ac:dyDescent="0.25" spans="1:10">
@@ -2678,28 +2681,28 @@
         <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E78" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F78" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G78" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H78" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I78" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J78" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" x14ac:dyDescent="0.25" spans="1:10">
@@ -2710,28 +2713,28 @@
         <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E79" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F79" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G79" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H79" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J79" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" x14ac:dyDescent="0.25" spans="1:10">
@@ -2742,28 +2745,28 @@
         <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E80" t="s">
+        <v>26</v>
+      </c>
+      <c r="F80" t="s">
+        <v>27</v>
+      </c>
+      <c r="G80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H80" t="s">
+        <v>69</v>
+      </c>
+      <c r="I80" t="s">
         <v>25</v>
       </c>
-      <c r="F80" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" t="s">
-        <v>67</v>
-      </c>
-      <c r="H80" t="s">
-        <v>68</v>
-      </c>
-      <c r="I80" t="s">
-        <v>47</v>
-      </c>
       <c r="J80" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" x14ac:dyDescent="0.25" spans="1:10">
@@ -2774,28 +2777,28 @@
         <v>11</v>
       </c>
       <c r="C81" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" t="s">
+        <v>15</v>
+      </c>
+      <c r="E81" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" t="s">
+        <v>21</v>
+      </c>
+      <c r="G81" t="s">
+        <v>68</v>
+      </c>
+      <c r="H81" t="s">
+        <v>69</v>
+      </c>
+      <c r="I81" t="s">
         <v>31</v>
       </c>
-      <c r="D81" t="s">
-        <v>32</v>
-      </c>
-      <c r="E81" t="s">
-        <v>37</v>
-      </c>
-      <c r="F81" t="s">
-        <v>38</v>
-      </c>
-      <c r="G81" t="s">
-        <v>67</v>
-      </c>
-      <c r="H81" t="s">
-        <v>68</v>
-      </c>
-      <c r="I81" t="s">
-        <v>27</v>
-      </c>
       <c r="J81" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" x14ac:dyDescent="0.25" spans="1:10">
@@ -2806,28 +2809,28 @@
         <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E82" t="s">
+        <v>29</v>
+      </c>
+      <c r="F82" t="s">
+        <v>30</v>
+      </c>
+      <c r="G82" t="s">
+        <v>68</v>
+      </c>
+      <c r="H82" t="s">
+        <v>69</v>
+      </c>
+      <c r="I82" t="s">
         <v>28</v>
       </c>
-      <c r="F82" t="s">
-        <v>29</v>
-      </c>
-      <c r="G82" t="s">
-        <v>67</v>
-      </c>
-      <c r="H82" t="s">
-        <v>68</v>
-      </c>
-      <c r="I82" t="s">
-        <v>39</v>
-      </c>
       <c r="J82" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" x14ac:dyDescent="0.25" spans="1:10">
@@ -2838,28 +2841,28 @@
         <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D83" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E83" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F83" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G83" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I83" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J83" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" x14ac:dyDescent="0.25" spans="1:10">
@@ -2870,28 +2873,28 @@
         <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D84" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E84" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F84" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G84" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I84" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J84" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" x14ac:dyDescent="0.25" spans="1:10">
@@ -2902,28 +2905,28 @@
         <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D85" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E85" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F85" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H85" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I85" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J85" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" x14ac:dyDescent="0.25" spans="1:10">
@@ -2934,28 +2937,28 @@
         <v>11</v>
       </c>
       <c r="C86" t="s">
+        <v>26</v>
+      </c>
+      <c r="D86" t="s">
+        <v>27</v>
+      </c>
+      <c r="E86" t="s">
+        <v>38</v>
+      </c>
+      <c r="F86" t="s">
+        <v>39</v>
+      </c>
+      <c r="G86" t="s">
+        <v>70</v>
+      </c>
+      <c r="H86" t="s">
+        <v>71</v>
+      </c>
+      <c r="I86" t="s">
         <v>34</v>
       </c>
-      <c r="D86" t="s">
-        <v>35</v>
-      </c>
-      <c r="E86" t="s">
-        <v>37</v>
-      </c>
-      <c r="F86" t="s">
-        <v>38</v>
-      </c>
-      <c r="G86" t="s">
-        <v>69</v>
-      </c>
-      <c r="H86" t="s">
-        <v>70</v>
-      </c>
-      <c r="I86" t="s">
-        <v>30</v>
-      </c>
       <c r="J86" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" x14ac:dyDescent="0.25" spans="1:10">
@@ -2966,28 +2969,28 @@
         <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D87" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E87" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F87" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G87" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H87" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I87" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J87" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" x14ac:dyDescent="0.25" spans="1:10">
@@ -2998,28 +3001,28 @@
         <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D88" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E88" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F88" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G88" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I88" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="J88" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" x14ac:dyDescent="0.25" spans="1:10">
@@ -3030,28 +3033,28 @@
         <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D89" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E89" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F89" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G89" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H89" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I89" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J89" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" x14ac:dyDescent="0.25" spans="1:10">
@@ -3062,28 +3065,28 @@
         <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D90" t="s">
+        <v>27</v>
+      </c>
+      <c r="E90" t="s">
         <v>35</v>
       </c>
-      <c r="E90" t="s">
-        <v>31</v>
-      </c>
       <c r="F90" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G90" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I90" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J90" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" x14ac:dyDescent="0.25" spans="1:10">
@@ -3094,28 +3097,28 @@
         <v>11</v>
       </c>
       <c r="C91" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D91" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E91" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F91" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G91" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I91" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="J91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
